--- a/Templates~/Config/Excels/UI/UISprite.xlsx
+++ b/Templates~/Config/Excels/UI/UISprite.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Workspace\Unity\Game Dev Tools\Packages\com.moirai.framework\Templates~\Config\Excels\UI\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Workspace\Unity\Game Dev Tools\Client\Packages\com.moirai.framework\Templates~\Config\Excels\UI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E419F786-D108-463C-A865-9B32B4722628}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F961851-5819-4065-A29B-654AFF34661F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4635" yWindow="4635" windowWidth="28815" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4980" yWindow="4980" windowWidth="28815" windowHeight="15345" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SpriteConfig" sheetId="1" r:id="rId1"/>
@@ -106,18 +106,6 @@
     <t>ui</t>
   </si>
   <si>
-    <t>Assets/AssetRaw/Icon/Atlas/icon_item.spriteatlasv2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Assets/AssetRaw/Icon/Atlas/icon_ability.spriteatlasv2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Assets/AssetRaw/Icon/Atlas/icon_status.spriteatlasv2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>ui</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -137,10 +125,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Assets/AssetRaw/UI/Atlas/Cyberpunk GUI.spriteatlasv2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>item_00001</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -154,6 +138,22 @@
   </si>
   <si>
     <t>stats_health</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/AssetRaw/Default/Icon/Atlas/icon_item.spriteatlasv2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/AssetRaw/Default/Icon/Atlas/icon_ability.spriteatlasv2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/AssetRaw/Default/Icon/Atlas/icon_status.spriteatlasv2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/AssetRaw/Default/UI/Atlas/GUI.spriteatlasv2</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -586,10 +586,10 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B5" s="3" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>17</v>
@@ -598,13 +598,13 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B6" s="3" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -693,34 +693,34 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B5" s="3" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B6" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B7" s="3" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B8" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
